--- a/cuadros/JUNIO/GUACARA.xlsx
+++ b/cuadros/JUNIO/GUACARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260604164859</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>001107</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GABRIELA A. VIVAS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>no se completa la fiscalización y se borro</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_071539_0.png</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260605071539</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/GUACARA.xlsx
+++ b/cuadros/JUNIO/GUACARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260605071539</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>001107</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ELIANNYS VILLEGAS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>no se realizo el proceso y se elimino la fiscalización</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>INC_074621_0.png</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ID_20260608074621</t>
         </is>
       </c>
     </row>
